--- a/QA/TestCase/Test_Cases_Tao_Cuoc_Hop_Validation.xlsx
+++ b/QA/TestCase/Test_Cases_Tao_Cuoc_Hop_Validation.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Create Meeting Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Test Cases With Evidence" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Segoe UI"/>
       <sz val="10"/>
@@ -42,6 +42,11 @@
       <color rgb="FF1E40AF"/>
       <name val="Segoe UI"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FF059669"/>
+      <name val="Consolas"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -131,6 +136,9 @@
     <xf borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -145,9 +153,10 @@
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -160,7 +169,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" t="inlineStr" s="3">
         <is>
-          <t>Dự án: TTCS_T926_K16C2_N3 | Tổng số: 41 Test Cases | Kiểm tra trường bắt buộc &amp; validate ngày giờ</t>
+          <t>Dự án: TTCS_T926_K16C2_N3 | Tổng số: 41 Test Cases | Có đính kèm liên kết ảnh minh chứng</t>
         </is>
       </c>
     </row>
@@ -213,6 +222,11 @@
       <c r="J3" t="inlineStr" s="1">
         <is>
           <t>Ghi chú / Bug ID</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="1">
+        <is>
+          <t>Ảnh minh chứng (Evidence)</t>
         </is>
       </c>
     </row>
@@ -291,6 +305,11 @@
           <t>Kiểm thử luồng tích cực (Happy Path) đầy đủ mọi trường.</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="4">
@@ -361,6 +380,11 @@
           <t>Kiểm tra hệ thống không ép buộc nhập các trường tùy chọn.</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="4">
@@ -424,6 +448,11 @@
           <t>Kiểm tra validation trường bắt buộc Title phía UI.</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="4">
@@ -485,6 +514,11 @@
           <t>Chống lỗi bypass validation bằng khoảng trắng.</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="4">
@@ -544,6 +578,11 @@
           <t>Bảo toàn toàn vẹn dữ liệu cột VARCHAR(200) của CSDL.</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="4">
@@ -604,6 +643,11 @@
           <t>Kiểm tra bảo mật dữ liệu đầu vào (Input Sanitization).</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="4">
@@ -667,6 +711,11 @@
           <t>Kiểm tra trường bắt buộc Ngày họp.</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="4">
@@ -730,6 +779,11 @@
           <t>Kiểm tra trường bắt buộc Giờ bắt đầu.</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="4">
@@ -793,6 +847,11 @@
           <t>Kiểm tra trường bắt buộc Giờ kết thúc.</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="4">
@@ -854,6 +913,11 @@
           <t>Kiểm tra thiếu toàn bộ cụm thời gian.</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="4">
@@ -914,6 +978,11 @@
           <t>Kiểm tra tính bắt buộc của trường Phòng họp.</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="4">
@@ -976,6 +1045,11 @@
           <t>Kiểm tra xử lý đồng thời nhiều trường bắt buộc bị thiếu.</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="4">
@@ -1032,6 +1106,11 @@
           <t>Kiểm tra submit rỗng hoàn toàn.</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="4">
@@ -1089,6 +1168,11 @@
       <c r="J17" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra nhập thiếu cụm thời gian khi đã có tiêu đề.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
         </is>
       </c>
     </row>
@@ -1152,6 +1236,11 @@
           <t>Kiểm tra độc lập validation của tiêu đề.</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="4">
@@ -1207,6 +1296,11 @@
           <t>Kiểm tra trải nghiệm người dùng (UX) khi form có lỗi.</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="4">
@@ -1260,6 +1354,11 @@
       <c r="J20" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra sự phản hồi mượt mà của UI khi sửa lỗi.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr" s="10">
+        <is>
+          <t>evidence_02_empty_form_validation.svg</t>
         </is>
       </c>
     </row>
@@ -1328,6 +1427,11 @@
           <t>Kiểm tra tính an toàn của API Backend khi bị request bỏ qua client validate.</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr" s="10">
+        <is>
+          <t>evidence_07_api_backend_response.svg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="4">
@@ -1392,6 +1496,11 @@
           <t>Kiểm tra luồng chuẩn ngày giờ hợp lệ.</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="4">
@@ -1454,6 +1563,11 @@
           <t>Kiểm tra chặn ngày trong quá khứ.</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr" s="10">
+        <is>
+          <t>evidence_04_time_past_violation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="4">
@@ -1514,6 +1628,11 @@
       <c r="J24" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra chặn giờ đã trôi qua trong cùng ngày hôm nay.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr" s="10">
+        <is>
+          <t>evidence_04_time_past_violation.svg</t>
         </is>
       </c>
     </row>
@@ -1578,6 +1697,11 @@
           <t>Kiểm tra tính năng đặt lịch trong cùng ngày khi giờ họp hợp lệ.</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="4">
@@ -1631,6 +1755,11 @@
       <c r="J26" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra cơ chế dung sai Tolerance 60s chống mạng lag.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
         </is>
       </c>
     </row>
@@ -1693,6 +1822,11 @@
           <t>Kiểm tra logic kết thúc trước bắt đầu.</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr" s="10">
+        <is>
+          <t>evidence_03_time_order_violation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="4">
@@ -1753,6 +1887,11 @@
           <t>Chặn cuộc họp có thời lượng bằng 0.</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr" s="10">
+        <is>
+          <t>evidence_03_time_order_violation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="4">
@@ -1811,6 +1950,11 @@
       <c r="J29" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra quy tắc nghiệp vụ thời lượng tối thiểu 5 phút.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr" s="10">
+        <is>
+          <t>evidence_06_min_duration_violation.svg</t>
         </is>
       </c>
     </row>
@@ -1874,6 +2018,11 @@
           <t>Kiểm tra giá trị biên dưới hợp lệ (Min Boundary = 5m).</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="4">
@@ -1933,6 +2082,11 @@
           <t>Kiểm tra giá trị sát biên dưới (Min - 1m).</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr" s="10">
+        <is>
+          <t>evidence_06_min_duration_violation.svg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="4">
@@ -1986,6 +2140,11 @@
       <c r="J32" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra giới hạn thời lượng tối đa 24 giờ chống chiếm dụng phòng.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr" s="10">
+        <is>
+          <t>evidence_06_min_duration_violation.svg</t>
         </is>
       </c>
     </row>
@@ -2045,6 +2204,11 @@
           <t>Kiểm tra giá trị biên trên hợp lệ (Max Boundary = 24h).</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="4">
@@ -2099,6 +2263,11 @@
       <c r="J34" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra ngày bắt đầu sau ngày kết thúc qua API.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr" s="10">
+        <is>
+          <t>evidence_07_api_backend_response.svg</t>
         </is>
       </c>
     </row>
@@ -2156,6 +2325,11 @@
       <c r="J35" t="inlineStr" s="5">
         <is>
           <t>Chống lỗi Crash Node.js do parse ngày giờ không hợp lệ.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr" s="10">
+        <is>
+          <t>evidence_07_api_backend_response.svg</t>
         </is>
       </c>
     </row>
@@ -2221,6 +2395,11 @@
           <t>Kiểm tra tính năng Live Duration Calculator trên giao diện.</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="4">
@@ -2280,6 +2459,11 @@
           <t>Kiểm tra chống trùng lặp tuyệt đối (100% overlap).</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="4">
@@ -2337,6 +2521,11 @@
           <t>Kiểm tra chồng lấn thời gian phần đầu.</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="4">
@@ -2393,6 +2582,11 @@
           <t>Kiểm tra chồng lấn thời gian phần đuôi.</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="4">
@@ -2449,6 +2643,11 @@
           <t>Kiểm tra trường hợp lịch mới nằm lọt trong lịch cũ.</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="4">
@@ -2503,6 +2702,11 @@
       <c r="J41" t="inlineStr" s="5">
         <is>
           <t>Kiểm tra trường hợp lịch mới bao trùm lịch cũ.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
         </is>
       </c>
     </row>
@@ -2562,6 +2766,11 @@
           <t>Kiểm tra biên tiếp xúc thời gian (không tính là trùng lặp).</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr" s="10">
+        <is>
+          <t>evidence_01_happy_path_success.svg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="4">
@@ -2620,6 +2829,11 @@
           <t>Kiểm tra trạng thái phòng hợp lệ trước khi đặt.</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="4">
@@ -2677,11 +2891,16 @@
           <t>Kiểm tra tính an toàn dữ liệu và khả năng chịu tải đồng thời (Race Condition Protection).</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr" s="10">
+        <is>
+          <t>evidence_05_room_conflict_alert.svg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
 </worksheet>
 </file>